--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -13,8 +13,8 @@
     <sheet name="추적매트릭스" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">요구사항정의서!$A$4:$G$20</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">테스트케이스!$A$4:$L$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">요구사항정의서!$A$4:$G$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">테스트케이스!$A$4:$L$20</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="213">
   <si>
     <r>
       <rPr>
@@ -58,7 +58,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">공개 샌드박스</t>
+      <t xml:space="preserve">티맵풍 데모 앱</t>
     </r>
     <r>
       <rPr>
@@ -68,7 +68,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -77,7 +77,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">목킹 기준 데모 </t>
+      <t xml:space="preserve">로그인→경로검색</t>
     </r>
     <r>
       <rPr>
@@ -87,7 +87,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· </t>
+      <t xml:space="preserve">)/reqres/</t>
     </r>
     <r>
       <rPr>
@@ -96,7 +96,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">우선순위 </t>
+      <t xml:space="preserve">목킹 기준 </t>
     </r>
     <r>
       <rPr>
@@ -106,21 +106,1023 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">P1(High)~P3(Low) · ISO/IEC 25010 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경로검색</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
+      <t xml:space="preserve">· P1(High)~P3(Low) · ISO/IEC 25010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구사항 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">요구사항 설명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인수 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Acceptance Criteria)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">우선순위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구분</t>
+  </si>
+  <si>
+    <t xml:space="preserve">품질특성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-AUTH-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인증 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그인</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">유효한 계정으로 로그인하면 경로검색 화면으로 진입해야 한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 성공 시 경로검색 화면 노출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기능적합성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-AUTH-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잘못된 자격증명은 로그인이 차단되고 오류가 안내되어야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">401 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">올바르지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">진입 차단</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">보안</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-AUTH-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필수 입력값 누락 시 적절한 안내를 표시해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아이디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">비밀번호 미입력 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력해 주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-API-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단일 사용자 조회 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 규격 응답을 반환해야 한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200, data.id/email/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이름 정합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-API-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">존재하지 않는 사용자 조회 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">404</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 처리해야 한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">미존재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">404</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">신뢰성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-API-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">생성</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 생성 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">201</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 생성 데이터를 반환해야 한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">201, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요청 반영 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ id/createdAt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">존재</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-API-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목록</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자 목록 조회 시 페이징 메타를 정확히 반환해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200, data </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배열 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ page/per_page/total </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조회</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경로 검색 정상 응답 시 경로 데이터가 규칙에 맞아야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">routes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최단경로 소요시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대안경로</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경로 검색 결과가 없을 때 빈 목록을 정상 처리해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">routes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빈 배열</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">([]) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반환 시 배열 타입 유지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-FAV-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">즐겨찾기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">즐겨찾기 목록 조회 시 규격에 맞는 항목을 반환해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">각 항목에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">name/lat/lng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">존재</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-FAV-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">즐겨찾기 추가 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">201</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 생성 결과를 반환해야 한다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">201, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요청</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(name/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">좌표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반영 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">발급</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-PLACE-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">장소추천 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로컬맛집</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">장소 추천 목록은 평점 내림차순으로 정렬되어야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">places</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rating </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내림차순 정합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과화면</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경로 검색 성공 시 결과 카드가 화면에 정확히 렌더링돼야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검색 시 경로 카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -129,17 +1131,15 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">즐겨찾기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소요시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -148,133 +1148,103 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장소추천은 목킹 시나리오</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요구사항 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ID</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">분류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">요구사항 설명</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인수 기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Acceptance Criteria)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">우선순위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구분</t>
-  </si>
-  <si>
-    <t xml:space="preserve">품질특성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-AUTH-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인증 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로그인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">유효한 계정으로 로그인하면 상품 목록으로 이동해야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정상 계정 입력 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">inventory </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">진입</t>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노출</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경로가 없을 때 사용자에게 안내 메시지를 표시해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빈 결과 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추천 경로가 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안내</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조회 오류 시 사용자에게 오류 메시지를 표시해야 한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5xx </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 시 오류 안내</t>
     </r>
     <r>
       <rPr>
@@ -291,845 +1261,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">목록 노출</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기능적합성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-AUTH-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">잠긴 계정은 로그인이 차단되고 사유가 안내되어야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">잠긴 계정 입력 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'locked out' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오류 노출</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">보안</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-AUTH-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">필수 입력값 누락 시 적절한 오류를 안내해야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">비밀번호 미입력 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'Password is required' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">노출</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-CART-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상품 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장바구니</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">상품을 장바구니에 담으면 수량이 정확히 반영되어야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">담기 후 배지 카운트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">증가</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-API-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API &gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단일 사용자 조회 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과 규격 응답을 반환해야 한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200, data.id/email/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이름 정합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-API-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">존재하지 않는 사용자 조회 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">404</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 처리해야 한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">미존재 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ID </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">404</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">신뢰성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-API-03</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API &gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">생성</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 생성 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">201</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과 생성 데이터를 반환해야 한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">201, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요청 반영 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ id/createdAt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">존재</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-API-04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">API &gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">목록</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사용자 목록 조회 시 페이징 메타를 정확히 반환해야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200, data </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배열 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ page/per_page/total </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-ROUTE-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경로검색 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조회</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">경로 검색 정상 응답 시 경로 데이터가 규칙에 맞아야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">routes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">최단경로 소요시간 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대안경로</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-ROUTE-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경로 검색 결과가 없을 때 빈 목록을 정상 처리해야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">routes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빈 배열</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">([]) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반환 시 배열 타입 유지</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">사용성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-FAV-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">경로검색 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">즐겨찾기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">즐겨찾기 목록 조회 시 규격에 맞는 항목을 반환해야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">각 항목에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">name/lat/lng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">존재</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-FAV-02</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">즐겨찾기 추가 시 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">201</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과 생성 결과를 반환해야 한다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">201, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요청</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(name/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">좌표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">반영 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ id </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">발급</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-PLACE-01</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장소추천 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로컬맛집</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장소 추천 목록은 평점 내림차순으로 정렬되어야 한다</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">places</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rating </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">내림차순 정합</t>
+      <t xml:space="preserve">카드 미노출</t>
     </r>
   </si>
   <si>
@@ -1453,7 +1585,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">16</t>
     </r>
     <r>
       <rPr>
@@ -1491,7 +1623,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">100% · </t>
+      <t xml:space="preserve">100% · Pass 100% · </t>
     </r>
     <r>
       <rPr>
@@ -1500,7 +1632,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">최종 판정 </t>
+      <t xml:space="preserve">판정 열은 </t>
     </r>
     <r>
       <rPr>
@@ -1510,7 +1642,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Pass 100% · </t>
+      <t xml:space="preserve">Pass/Fail </t>
     </r>
     <r>
       <rPr>
@@ -1519,25 +1651,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판정 열은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pass/Fail </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF808080"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">드롭다운</t>
     </r>
   </si>
@@ -1641,10 +1754,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">정상 계정 로그인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">로그인 페이지 접속</t>
+    <t xml:space="preserve">로그인 성공 진입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">앱 로그인 화면</t>
   </si>
   <si>
     <r>
@@ -1662,34 +1775,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">정상 계정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(standard_user) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
+      <t xml:space="preserve">아이디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -1707,6 +1802,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그인 클릭
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">3. </t>
     </r>
     <r>
@@ -1715,61 +1828,28 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">로그인 클릭</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상품 목록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Products)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">으로 이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, URL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">inventory.html</t>
-    </r>
+      <t xml:space="preserve">로그인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API 200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목킹</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경로검색 화면으로 진입</t>
   </si>
   <si>
     <t xml:space="preserve">Pass</t>
@@ -1828,7 +1908,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">잠긴 계정 로그인 차단</t>
+    <t xml:space="preserve">잘못된 자격증명 차단</t>
   </si>
   <si>
     <r>
@@ -1846,24 +1926,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">잠긴 계정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(locked_out_user) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력
+      <t xml:space="preserve">잘못된 계정 입력
 </t>
     </r>
     <r>
@@ -1881,26 +1944,78 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">로그인 클릭</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'locked out' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오류 노출</t>
+      <t xml:space="preserve">로그인 클릭
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API 401 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목킹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">올바르지 않습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오류</t>
     </r>
     <r>
       <rPr>
@@ -1989,17 +2104,16 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">아이디만 입력
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
+      <t xml:space="preserve">아이디</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -2017,6 +2131,187 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로그인 클릭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력해 주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">진입 차단</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-AUTH-03, REQ-COMPAT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-UI-004</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과화면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정상</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경로 결과 화면 렌더링</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 완료</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도착 입력
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검색 클릭
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">3. </t>
     </r>
     <r>
@@ -2025,42 +2320,104 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">로그인 클릭</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'Password is required' </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">오류 노출</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-AUTH-03, REQ-COMPAT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-UI-004</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상품 </t>
+      <t xml:space="preserve">경로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API 200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목킹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과 카드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건 렌더링</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최단 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분 표시</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-01, REQ-COMPAT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright + Mock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-UI-005</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
     </r>
     <r>
       <rPr>
@@ -2077,7 +2434,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">장바구니 </t>
+      <t xml:space="preserve">결과화면 </t>
     </r>
     <r>
       <rPr>
@@ -2094,14 +2451,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">담기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">장바구니 담기 수량 반영</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정상 로그인 상태</t>
+      <t xml:space="preserve">빈결과</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">경로 없음 화면 안내</t>
   </si>
   <si>
     <r>
@@ -2119,7 +2473,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">상품 목록 진입
+      <t xml:space="preserve">검색 클릭
 </t>
     </r>
     <r>
@@ -2137,55 +2491,232 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">첫 상품 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Add to cart </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">클릭</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장바구니 배지 카운트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">증가</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">REQ-CART-01, REQ-COMPAT-01</t>
+      <t xml:space="preserve">빈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">routes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목킹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추천 경로가 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-02, REQ-COMPAT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-UI-006</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로검색 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">결과화면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오류</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">조회 오류 화면 안내</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">검색 클릭
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. 503 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목킹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">오류 안내 메시지 표시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">카드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-ROUTE-UI-03, REQ-COMPAT-01</t>
   </si>
   <si>
     <t xml:space="preserve">TC-API-001</t>
@@ -3298,7 +3829,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">경로 없음 처리</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로 없음 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(API)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3538,7 +4085,23 @@
     <t xml:space="preserve">경로 검색 정상 응답</t>
   </si>
   <si>
-    <t xml:space="preserve">경로 검색 빈 결과 처리</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">경로 검색 빈 결과 처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(API)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3775,7 +4338,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TC-UI-001~004</t>
+    <t xml:space="preserve">TC-UI-001~006</t>
   </si>
   <si>
     <t xml:space="preserve">커버리지 요약</t>
@@ -4401,12 +4964,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
@@ -4468,7 +5031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -4478,7 +5041,7 @@
       <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -4514,21 +5077,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
+      <c r="E8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>14</v>
@@ -4542,22 +5105,22 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
+      <c r="E9" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,22 +5128,22 @@
         <v>32</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
+      <c r="D10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4596,8 +5159,8 @@
       <c r="D11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>14</v>
@@ -4606,11 +5169,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -4619,8 +5182,8 @@
       <c r="D12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>23</v>
+      <c r="E12" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>14</v>
@@ -4629,64 +5192,64 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="8" t="s">
         <v>51</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
@@ -4700,10 +5263,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>58</v>
@@ -4721,7 +5284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>60</v>
       </c>
@@ -4731,11 +5294,11 @@
       <c r="C17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>23</v>
+      <c r="E17" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>14</v>
@@ -4744,77 +5307,123 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>78</v>
       </c>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G20"/>
+  <autoFilter ref="A4:G22"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4831,7 +5440,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -4849,35 +5458,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>6</v>
@@ -4892,30 +5501,30 @@
         <v>2</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>13</v>
@@ -4927,33 +5536,33 @@
         <v>15</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="E6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>13</v>
@@ -4965,33 +5574,33 @@
         <v>19</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>23</v>
@@ -5003,36 +5612,36 @@
         <v>15</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
+        <v>100</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>14</v>
@@ -5041,71 +5650,71 @@
         <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>123</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>13</v>
+        <v>100</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>121</v>
+        <v>14</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>129</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>23</v>
@@ -5114,74 +5723,74 @@
         <v>14</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>23</v>
@@ -5190,36 +5799,36 @@
         <v>14</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L12" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>13</v>
@@ -5231,74 +5840,74 @@
         <v>15</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>141</v>
+        <v>153</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>23</v>
+        <v>100</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>14</v>
@@ -5307,71 +5916,71 @@
         <v>15</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>23</v>
@@ -5383,54 +5992,130 @@
         <v>15</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>51</v>
+        <v>100</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="K18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>144</v>
+      <c r="K20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L18"/>
+  <autoFilter ref="A4:L20"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G18" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G20" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5451,10 +6136,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
@@ -5463,12 +6148,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5482,13 +6167,13 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5496,19 +6181,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5516,19 +6201,19 @@
         <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5536,19 +6221,19 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5556,19 +6241,19 @@
         <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5576,19 +6261,19 @@
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5596,19 +6281,19 @@
         <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5616,19 +6301,19 @@
         <v>36</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5636,19 +6321,19 @@
         <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5656,39 +6341,39 @@
         <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5696,168 +6381,208 @@
         <v>53</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>183</v>
+        <v>67</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <f aca="false">COUNTA(A5:A20)</f>
-        <v>16</v>
+      <c r="A22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <f aca="false">COUNTIF(E5:E20,"Y")</f>
-        <v>16</v>
+      <c r="A24" s="11" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="13" t="n">
-        <f aca="false">COUNTIF(E5:E20,"Y")/COUNTA(A5:A20)</f>
+        <v>208</v>
+      </c>
+      <c r="B25" s="12" t="n">
+        <f aca="false">COUNTA(A5:A22)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B26" s="12" t="n">
+        <f aca="false">COUNTIF(E5:E22,"Y")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <f aca="false">COUNTIF(E5:E22,"Y")/COUNTA(A5:A22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="B26" s="14" t="n">
-        <f aca="false">COUNTIF(F5:F20,"Pass")</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B27" s="13" t="n">
-        <f aca="false">COUNTIF(F5:F20,"Pass")/COUNTA(F5:F20)</f>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <f aca="false">COUNTIF(F5:F22,"Pass")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <f aca="false">COUNTIF(F5:F22,"Pass")/COUNTA(F5:F22)</f>
         <v>1</v>
       </c>
     </row>
